--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS GENERAL SEASON ARCHERY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS GENERAL SEASON ARCHERY.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -657,7 +662,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -730,7 +736,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -802,8 +809,13 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -868,7 +880,8 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -936,8 +949,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -1010,7 +1028,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -1075,7 +1094,8 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1152,7 +1172,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1229,7 +1250,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
